--- a/Testes/reescala/Teste populacao e gerações/Teste5/3_melhor_escala.xlsx
+++ b/Testes/reescala/Teste populacao e gerações/Teste5/3_melhor_escala.xlsx
@@ -1405,8 +1405,8 @@
       <c r="P8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="5" t="n">
-        <v>0</v>
+      <c r="Q8" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R8" s="5" t="n">
         <v>0</v>
@@ -3229,11 +3229,11 @@
       <c r="AF24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="4" t="n">
-        <v>1</v>
+      <c r="AG24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI24" s="5" t="n">
         <v>0</v>
@@ -3625,8 +3625,8 @@
       <c r="P28" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" s="4" t="n">
-        <v>1</v>
+      <c r="Q28" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R28" s="4" t="n">
         <v>1</v>
@@ -4180,8 +4180,8 @@
       <c r="P33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" s="4" t="n">
-        <v>1</v>
+      <c r="Q33" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R33" s="4" t="n">
         <v>1</v>
@@ -4561,11 +4561,11 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI36" s="5" t="n">
         <v>0</v>
@@ -4744,11 +4744,11 @@
       <c r="S38" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="4" t="n">
-        <v>1</v>
+      <c r="T38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="V38" s="5" t="n">
         <v>0</v>
@@ -4846,8 +4846,8 @@
       <c r="P39" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q39" s="5" t="n">
-        <v>0</v>
+      <c r="Q39" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R39" s="4" t="n">
         <v>1</v>
@@ -4957,8 +4957,8 @@
       <c r="P40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" s="4" t="n">
-        <v>1</v>
+      <c r="Q40" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R40" s="4" t="n">
         <v>1</v>
@@ -5068,8 +5068,8 @@
       <c r="P41" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" s="5" t="n">
-        <v>0</v>
+      <c r="Q41" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R41" s="5" t="n">
         <v>0</v>
@@ -5401,8 +5401,8 @@
       <c r="P44" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" s="4" t="n">
-        <v>1</v>
+      <c r="Q44" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R44" s="4" t="n">
         <v>1</v>
@@ -5410,11 +5410,11 @@
       <c r="S44" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" s="5" t="n">
-        <v>0</v>
+      <c r="T44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="V44" s="5" t="n">
         <v>0</v>
@@ -5956,8 +5956,8 @@
       <c r="P49" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" s="5" t="n">
-        <v>0</v>
+      <c r="Q49" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R49" s="4" t="n">
         <v>1</v>
